--- a/docs/validation/classeurs/validation_niveau_de_vie.xlsx
+++ b/docs/validation/classeurs/validation_niveau_de_vie.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation'!$A$1:$S$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation'!$A$1:$U$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -211,7 +211,7 @@
     <author>session mère</author>
   </authors>
   <commentList>
-    <comment ref="R1" authorId="0" shapeId="0">
+    <comment ref="T1" authorId="0" shapeId="0">
       <text>
         <t>À remplir seulement si vous divergez de la décision par défaut. Liste : retenu, retenu_socle, ecarte, a_discuter.</t>
       </text>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1. Ouvrez l'onglet « Validation ». Chaque ligne est un indicateur candidat (une fiche YAML dans le dépôt), regroupé par famille ; la variante principale de chaque famille est en tête.</t>
+          <t>1. Ouvrez l'onglet « Validation ». Chaque ligne est un indicateur candidat (une fiche YAML dans le dépôt), regroupé par sous-thème puis par famille ; la variante principale de chaque famille est en tête.</t>
         </is>
       </c>
     </row>
@@ -549,102 +549,116 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3. Ne remplissez la colonne jaune « Votre décision » que là où vous divergez ou hésitez. Valeurs possibles (liste déroulante) :</t>
+          <t xml:space="preserve">   « Socle proposé » = oui : l'agent propose de cocher l'indicateur par défaut (décision D41 : les incontournables et une fiche principale par sous-thème de la dimension, 8 au plus) ; sa décision par défaut est alors retenu_socle. L'onglet « Synthèse » compte le socle par sous-thème.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">     retenu = disponible dans l'outil, non coché par défaut ;</t>
+          <t>3. Ne remplissez la colonne jaune « Votre décision » que là où vous divergez ou hésitez. Valeurs possibles (liste déroulante) :</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">     retenu_socle = disponible ET coché par défaut dans la configuration de référence ;</t>
+          <t xml:space="preserve">     retenu = disponible dans l'outil, non coché par défaut ;</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">     ecarte = non retenu (indiquez pourquoi dans le commentaire) ;</t>
+          <t xml:space="preserve">     retenu_socle = disponible ET coché par défaut dans la configuration de référence ;</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">     a_discuter = vous voulez en parler avant de trancher (la session mère vous posera la question).</t>
+          <t xml:space="preserve">     ecarte = non retenu (indiquez pourquoi dans le commentaire) ;</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>4. Le commentaire est libre ; il est lu et conservé dans la fiche.</t>
+          <t xml:space="preserve">     a_discuter = vous voulez en parler avant de trancher (la session mère vous posera la question).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>4. Le commentaire est libre ; il est lu et conservé dans la fiche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>5. Enregistrez le fichier au même endroit, sous le même nom : la session mère le relit automatiquement.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-    </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Rappels</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>— Une famille regroupe des variantes d'un même concept (autre seuil, autre source, ventilation) : en général une seule variante est cochée par défaut.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>— « Incontournable » = présent dans au moins trois cadres de référence (Doughnut, Stiglitz-Sen-Fitoussi, OCDE, Eurostat, INSEE).</t>
+          <t>— Une famille regroupe des variantes d'un même concept (autre seuil, autre source, ventilation) : en général une seule variante est cochée par défaut.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>— « Déclaratif » = donnée d'enquête d'opinion ou de ressenti ; « Composite » = indice agrégé d'un producteur tiers (V-Dem, CPI…).</t>
+          <t>— Le socle est une proposition : pour l'élargir, mettez retenu_socle sur d'autres lignes ; pour le réduire, mettez retenu sur une ligne proposée.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>— Sens « ambigu » : l'agent n'a pas pu établir si plus haut est mieux ; ces lignes sont écartées par défaut.</t>
+          <t>— « Incontournable » = présent dans au moins trois cadres de référence (Doughnut, Stiglitz-Sen-Fitoussi, OCDE, Eurostat, INSEE).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>— Les bornes (seuil minimal, objectif) ne sont pas traitées ici : elles viendront après le gel 2 (socle v1).</t>
+          <t>— « Déclaratif » = donnée d'enquête d'opinion ou de ressenti ; « Composite » = indice agrégé d'un producteur tiers (V-Dem, CPI…).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>— Sens « ambigu » : l'agent n'a pas pu établir si plus haut est mieux ; ces lignes sont écartées par défaut.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>— Les bornes (seuil minimal, objectif) ne sont pas traitées ici : elles viendront après le gel 2 (socle v1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Exemple de ligne remplie : décision « ecarte », commentaire « doublon de la série INSEE équivalente ; garder la variante INSEE ».</t>
         </is>
@@ -661,122 +675,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="70" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>Sous-thème</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>Famille</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Identifiant</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Libellé</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Variante principale</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Définition courte</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Sens</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Unité</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Série (identifiant)</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Période</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Déclaratif</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Composite</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Incontournable</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Socle proposé</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Recommandation de l'agent</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Motif de la recommandation</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Décision par défaut (si vous ne remplissez rien)</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Votre décision (liste déroulante)</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>Votre commentaire</t>
         </is>
@@ -785,64 +811,64 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>consommation_menages</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>consommation_effective_habitant</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Consommation individuelle effective par habitant en volume</t>
+          <t>accès à l'alimentation</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>privation_alimentaire</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>privation_alimentaire</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Ne pas avoir les moyens d'un repas avec viande, poisson ou équivalent un jour sur deux</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Biens et services consommés par les ménages, qu'ils les paient eux-mêmes ou qu'ils soient financés par les administrations ou les institutions sans but lucratif (santé, éducation, logement social…), rapportés à la …</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>haut</t>
+          <t>Part des personnes vivant dans un ménage qui n'a pas les moyens de s'offrir un repas comportant de la viande, du poulet ou du poisson (ou un équivalent végétarien) au moins un jour sur deux (EU-SILC, élément de la …</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>euros de 2020 par habitant</t>
+          <t>bas</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Eurostat — nama_10_pc (PIB et principales composantes par habitant), na_item P41</t>
+          <t>% de la population</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>nama_10_pc?freq=A&amp;unit=CLV20_EUR_HAB&amp;na_item=P41&amp;geo=FR</t>
+          <t>Eurostat — ilc_mdes03 (incapacité à s'offrir un repas comportant de la viande, du poulet ou du poisson un jour sur deux, enquêtes EU-SILC), ensemble des ménages</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>2000-2025 (26 points, annuelle)</t>
+          <t>ilc_mdes03?freq=A&amp;hhcomp=TOTAL&amp;rskpovth=TOTAL&amp;unit=PC&amp;geo=FR</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
+          <t>2004-2025 (22 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -855,83 +881,93 @@
       </c>
       <c r="O2" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
           <t>retenir</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>Mesure de la consommation retenue par Stiglitz-Sen-Fitoussi et le cadre Qualité de vie d'Eurostat, en niveau par habitant et en volume de 2000 à 2025 (26 points), que l'INSEE ne publie qu'en total.</t>
-        </is>
-      </c>
-      <c r="Q2" s="5" t="inlineStr">
-        <is>
-          <t>retenu</t>
-        </is>
-      </c>
-      <c r="R2" s="7" t="inlineStr"/>
-      <c r="S2" s="7" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>Seule mesure annuelle de l'accès à l'alimentation (A2), publiée par Eurostat de 2004 à 2025 (22 points), plus longue de 6 ans et plus fraîche d'un an que l'indicateur ODD 2.i1 de l'INSEE, dont elle ne s'écarte pas de plus de 0,2 point sur 2010-2024 (méthode §4).</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>retenu_socle</t>
+        </is>
+      </c>
+      <c r="T2" s="7" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>depenses_pre_engagees</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>depenses_pre_engagees</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Part des dépenses pré-engagées dans le revenu disponible des ménages</t>
+          <t>consommation</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>consommation_menages</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>consommation_effective_habitant</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Consommation individuelle effective par habitant en volume</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Part, dans le revenu disponible brut des ménages, des dépenses réalisées dans le cadre d'un contrat difficilement renégociable à court terme : logement (y compris loyers imputés), eau, énergie, télécommunications, …</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>bas</t>
+          <t>Biens et services consommés par les ménages, qu'ils les paient eux-mêmes ou qu'ils soient financés par les administrations ou les institutions sans but lucratif (santé, éducation, logement social…), rapportés à la …</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>% du revenu disponible brut</t>
+          <t>haut</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>INSEE — Melodi DD_CNA_AGREGATS (comptes nationaux annuels, base 2020), mesure _DEP_REVENU</t>
+          <t>euros de 2020 par habitant</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>DD_CNA_AGREGATS?ACCOUNTING_ENTRY=_Z&amp;ACTIVITY=_T&amp;COUNTERPART_AREA=W2&amp;EXPENDITURE=CPDPE&amp;FREQ=A&amp;GEO=FRANCE-F&amp;INSTR_ASSET=_Z&amp;PRICES=V&amp;PRODUCT=_T&amp;REF_SECTOR=S14&amp;REF_YEAR_PRICE=&amp;STO=_DEP_REVENU&amp;TRANSFORMATION=N&amp;UNIT_MEASURE=PT</t>
+          <t>Eurostat — nama_10_pc (PIB et principales composantes par habitant), na_item P41</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>1959-2025 (26 points, annuelle)</t>
+          <t>nama_10_pc?freq=A&amp;unit=CLV20_EUR_HAB&amp;na_item=P41&amp;geo=FR</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
+          <t>2000-2025 (26 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -944,83 +980,93 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
           <t>retenir</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>Mesure des dépenses contraintes, voisine de la « part des dépenses de base dans le budget » du cadre Qualité de vie d'Eurostat, publiée par l'INSEE de 1959 à 2025 (26 points).</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>Mesure de la consommation retenue par Stiglitz-Sen-Fitoussi et le cadre Qualité de vie d'Eurostat, en niveau par habitant et en volume de 2000 à 2025 (26 points), que l'INSEE ne publie qu'en total.</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R3" s="7" t="inlineStr"/>
-      <c r="S3" s="7" t="inlineStr"/>
+      <c r="T3" s="7" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>intensite_pauvrete</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>intensite_pauvrete</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Intensité de la pauvreté (seuil à 60 %)</t>
+          <t>consommation</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>depenses_pre_engagees</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>depenses_pre_engagees</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Part des dépenses pré-engagées dans le revenu disponible des ménages</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Écart relatif entre le niveau de vie médian des personnes pauvres et le seuil de pauvreté à 60 % du niveau de vie médian, en pourcentage du seuil (enquête Revenus fiscaux et sociaux, données rétropolées, France …</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
+          <t>Part, dans le revenu disponible brut des ménages, des dépenses réalisées dans le cadre d'un contrat difficilement renégociable à court terme : logement (y compris loyers imputés), eau, énergie, télécommunications, …</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
           <t>bas</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>% du seuil de pauvreté</t>
-        </is>
-      </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>INSEE — Melodi DS_ERFS_RETROPOLE (enquête ERFS, données rétropolées), mesure PI_MD60</t>
+          <t>% du revenu disponible brut</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>DS_ERFS_RETROPOLE?AGE=_T&amp;EMPSTA_ENQ=_T&amp;ERFS_MEASURE=PI_MD60&amp;GEO=FRANCE-FM&amp;MUN_DENSITY_LEVEL=_T&amp;TPH=_T</t>
+          <t>INSEE — Melodi DD_CNA_AGREGATS (comptes nationaux annuels, base 2020), mesure _DEP_REVENU</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>1996-2024 (25 points, annuelle)</t>
+          <t>DD_CNA_AGREGATS?ACCOUNTING_ENTRY=_Z&amp;ACTIVITY=_T&amp;COUNTERPART_AREA=W2&amp;EXPENDITURE=CPDPE&amp;FREQ=A&amp;GEO=FRANCE-F&amp;INSTR_ASSET=_Z&amp;PRICES=V&amp;PRODUCT=_T&amp;REF_SECTOR=S14&amp;REF_YEAR_PRICE=&amp;STO=_DEP_REVENU&amp;TRANSFORMATION=N&amp;UNIT_MEASURE=PT</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
+          <t>1959-2025 (26 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -1033,175 +1079,195 @@
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
           <t>retenir</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>Concept nommé dans le contenu de la dimension (« intensité de la pauvreté »), indicateur ODD 1.i3, publié sans rupture de 1996 à 2024 (25 points).</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>Mesure des dépenses contraintes, voisine de la « part des dépenses de base dans le budget » du cadre Qualité de vie d'Eurostat, publiée par l'INSEE de 1959 à 2025 (26 points).</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr"/>
-      <c r="S4" s="7" t="inlineStr"/>
+      <c r="T4" s="7" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>niveau_vie_median</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>niveau_vie_median</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Niveau de vie médian</t>
+          <t>opinions sur la société</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>perception_niveau_vie_france</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>pauvrete_percue_hausse</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Part des personnes estimant que la pauvreté a augmenté en France depuis cinq ans</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Niveau de vie (revenu disponible du ménage après impôts directs et prestations sociales, divisé par le nombre d'unités de consommation) qui partage la population en deux moitiés, en euros constants de la dernière année …</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>haut</t>
+          <t>Part des personnes interrogées par le baromètre d'opinion de la DREES qui répondent que la pauvreté et l'exclusion en France « ont augmenté » depuis cinq ans (question PE01, modalité 2), non-réponses incluses au …</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>euros constants par an et par unité de consommation</t>
+          <t>bas</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>INSEE — Melodi DS_ERFS_RETROPOLE (enquête ERFS, données rétropolées), mesure MED_SL</t>
+          <t>% des répondants</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>DS_ERFS_RETROPOLE?AGE=_T&amp;EMPSTA_ENQ=_T&amp;ERFS_MEASURE=MED_SL&amp;GEO=FRANCE-FM&amp;MUN_DENSITY_LEVEL=_T&amp;TPH=_T</t>
+          <t>DREES — Baromètre d'opinion de la DREES (data.drees, jeu 431_le-barometre-d-opinion), microdonnées pondérées</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>1996-2024 (25 points, annuelle)</t>
+          <t>data.drees.solidarites-sante.gouv.fr, jeu 431_le-barometre-d-opinion, pièce jointe barometre2000_2025_diff_csv ; variable PE01, modalité 2</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
+          <t>2000-2025 (25 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
           <t>retenir</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>Revenu médian des ménages, concept du cadre Qualité de vie d'Eurostat et de Stiglitz-Sen-Fitoussi (§5 du crosswalk), publié sans rupture par l'INSEE de 1996 à 2024 (25 points depuis 2000).</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="inlineStr">
-        <is>
-          <t>retenu_socle</t>
-        </is>
-      </c>
-      <c r="R5" s="7" t="inlineStr"/>
-      <c r="S5" s="7" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>Opinion sur la société (D32) portant sur la pauvreté, posée chaque année depuis 2000 sauf en 2003 (25 vagues), calculée sur microdonnées avec un contrôle de plausibilité sur la publication 2025 (D38 b), principale de la famille des perceptions du niveau de vie en France.</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>retenu</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>niveau_vie_modestes</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>niveau_vie_modestes</t>
+          <t>opinions sur la société</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>perception_niveau_vie_france</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Niveau de vie des plus modestes (premier décile)</t>
+          <t>solde_niveau_vie_france_futur</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Opinion des ménages sur l'évolution future du niveau de vie en France (solde)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Premier décile du niveau de vie : niveau de vie au-dessous duquel vivent les 10 % de personnes les plus modestes, en euros constants (enquête Revenus fiscaux et sociaux, données rétropolées, France métropolitaine).</t>
+          <t>non</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
+          <t>Solde des réponses (part des ménages jugeant que le niveau de vie en France va s'améliorer moins part jugeant qu'il va se détériorer) à la question sur les perspectives d'évolution du niveau de vie en France de …</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
           <t>haut</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>euros constants par an et par unité de consommation</t>
-        </is>
-      </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>INSEE — Melodi DS_ERFS_RETROPOLE (enquête ERFS, données rétropolées), mesure D1_SL</t>
+          <t>solde d'opinion (points de %)</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>DS_ERFS_RETROPOLE?AGE=_T&amp;EMPSTA_ENQ=_T&amp;ERFS_MEASURE=D1_SL&amp;GEO=FRANCE-FM&amp;MUN_DENSITY_LEVEL=_T&amp;TPH=_T</t>
+          <t>INSEE (enquête de conjoncture auprès des ménages) — BDM, enquête mensuelle de conjoncture auprès des ménages (ENQ-CONJ-MENAGES)</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>1996-2024 (25 points, annuelle)</t>
+          <t>000857177</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
+          <t>1970-2026 (mensuelle)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
@@ -1211,86 +1277,96 @@
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>retenir</t>
+          <t>non</t>
         </is>
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
-          <t>Seule mesure en euros constants du niveau de vie du bas de la distribution, publiée sans rupture de 1996 à 2024 (25 points depuis 2000), complémentaire du taux de pauvreté qui est relatif au médian.</t>
+          <t>non</t>
         </is>
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
+          <t>retenir_variante</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>Solde d'opinion mensuel de l'INSEE depuis 1970 sur les perspectives d'évolution du niveau de vie en France, admis comme variante déclarative par D38 (j), à agréger en moyenne annuelle.</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R6" s="7" t="inlineStr"/>
-      <c r="S6" s="7" t="inlineStr"/>
+      <c r="T6" s="7" t="inlineStr"/>
+      <c r="U6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>niveau_vie_modestes</t>
+          <t>opinions sur la société</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>pauvrete_ancree_2008</t>
+          <t>perception_niveau_vie_france</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Taux de pauvreté ancré dans le temps (seuil de 2008)</t>
+          <t>solde_niveau_vie_france_passe</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>Opinion des ménages sur l'évolution passée du niveau de vie en France (solde)</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Part des personnes dont le revenu disponible équivalent est inférieur au seuil de pauvreté de 2008 (60 % du revenu médian de 2008), réévalué de l'inflation (EU-SILC).</t>
+          <t>non</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>bas</t>
+          <t>Solde des réponses (part des ménages jugeant que le niveau de vie en France s'est amélioré moins part jugeant qu'il s'est détérioré) à la question sur l'évolution passée du niveau de vie en France de l'enquête mensuelle …</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>% de la population</t>
+          <t>haut</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Eurostat — ilc_li22b (taux de risque de pauvreté ancré en 2008, enquêtes EU-SILC)</t>
+          <t>solde d'opinion (points de %)</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>ilc_li22b?freq=A&amp;statinfo=MED_EI&amp;unit=PC&amp;rskpovth=B_60&amp;sex=T&amp;age=TOTAL&amp;geo=FR</t>
+          <t>INSEE (enquête de conjoncture auprès des ménages) — BDM, enquête mensuelle de conjoncture auprès des ménages (ENQ-CONJ-MENAGES)</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>2008-2025 (18 points, annuelle)</t>
+          <t>000857176</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
+          <t>1970-2026 (mensuelle)</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
@@ -1300,83 +1376,93 @@
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
           <t>retenir_variante</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>Indicateur de pauvreté « absolue » du cadre Qualité de vie d'Eurostat, annuel de 2008 à 2025 (18 points), lecture en taux du premier décile en euros constants, principal de la famille, mais dont la hausse tient aux ruptures d'EU-SILC de 2020 et 2022.</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>Solde d'opinion mensuel de l'INSEE depuis 1970 sur l'évolution passée du niveau de vie en France, admis comme variante déclarative par D38 (j), à agréger en moyenne annuelle.</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R7" s="7" t="inlineStr"/>
-      <c r="S7" s="7" t="inlineStr"/>
+      <c r="T7" s="7" t="inlineStr"/>
+      <c r="U7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>patrimoine_menages</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>patrimoine_net_median</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Patrimoine net médian des ménages</t>
+          <t>pauvreté et exclusion</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>pauvrete_exclusion_arope</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>pauvrete_exclusion_arope</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Personnes en risque de pauvreté ou d'exclusion sociale (AROPE)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Patrimoine net (actifs immobiliers, financiers et professionnels moins les dettes, hors « reste » : véhicules, équipement, objets de valeur) au-dessous duquel se situe la moitié des ménages, en euros constants (enquête …</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>haut</t>
+          <t>Part des personnes en risque de pauvreté (moins de 60 % du revenu médian), ou en situation de privation matérielle et sociale sévère, ou vivant dans un ménage à très faible intensité de travail (définition de la …</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>euros constants par ménage</t>
+          <t>bas</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>INSEE — Melodi DS_ENQPAT_DET (détention et montants du patrimoine des ménages), mesure MT_PATNET_HR_CST, médiane (D5), comparable depuis 2010</t>
+          <t>% de la population</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>DS_ENQPAT_DET?AGE=_T&amp;COMPARE_TIME=1_2010&amp;DEG_URB_UNIT=_T&amp;ENQPAT_MEASURE=MT_PATNET_HR_CST&amp;GEO=FRANCE-FM&amp;PCS=_T&amp;QUANTILE=D5&amp;QUANTILE_MEASURE=PATNET_HR_CST&amp;TPH=_T</t>
+          <t>Eurostat — sdg_01_10 (indicateur ODD de l'UE, définition 2030 ; doublon ilc_peps01n)</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>2010-2024 (5 points, irreguliere)</t>
+          <t>sdg_01_10?freq=A&amp;age=TOTAL&amp;unit=PC&amp;geo=FR</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
+          <t>2015-2025 (11 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -1384,88 +1470,98 @@
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
           <t>retenir</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
-          <t>Seule mesure du patrimoine du ménage médian (Stiglitz-Sen-Fitoussi, OCDE 1_3), cinq vagues de 2010 à 2024 admises comme série pluriannuelle (D17, D28 : écart moyen de 3,5 ans).</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="inlineStr">
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>Indicateur de l'objectif européen et français 2030 (−1,1 million de personnes en France par rapport à 2019, objectifs officiels du référentiel), annuel de 2015 à 2025 (11 points).</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
         <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R8" s="7" t="inlineStr"/>
-      <c r="S8" s="7" t="inlineStr"/>
+      <c r="T8" s="7" t="inlineStr"/>
+      <c r="U8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>pauvrete_enfants</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>taux_pauvrete_enfants</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Taux de pauvreté des enfants (moins de 18 ans, seuil à 60 %)</t>
+          <t>pauvreté monétaire</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>intensite_pauvrete</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>intensite_pauvrete</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Intensité de la pauvreté (seuil à 60 %)</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Part des personnes de moins de 18 ans vivant dans un ménage dont le niveau de vie est inférieur à 60 % du niveau de vie médian (enquête Revenus fiscaux et sociaux, données non rétropolées, France métropolitaine).</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
+          <t>Écart relatif entre le niveau de vie médian des personnes pauvres et le seuil de pauvreté à 60 % du niveau de vie médian, en pourcentage du seuil (enquête Revenus fiscaux et sociaux, données rétropolées, France …</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
           <t>bas</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>% des moins de 18 ans</t>
-        </is>
-      </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>INSEE — Melodi DS_ERFS_NON_RETROPOLE (enquête ERFS), mesure PR_MD60, âge Y_LT18, valeurs hors rupture (COMPARE_TIME = NB)</t>
+          <t>% du seuil de pauvreté</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>DS_ERFS_NON_RETROPOLE?AGE=Y_LT18&amp;COMPARE_TIME=NB&amp;EMPSTA_ENQ=_T&amp;ERFS_MEASURE=PR_MD60&amp;GEO=FRANCE-FM&amp;PCS=_T&amp;QUANTILE=_T&amp;SEX=_T&amp;TPH=_T</t>
+          <t>INSEE — Melodi DS_ERFS_RETROPOLE (enquête ERFS, données rétropolées), mesure PI_MD60</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>1996-2024 (22 points, annuelle)</t>
+          <t>DS_ERFS_RETROPOLE?AGE=_T&amp;EMPSTA_ENQ=_T&amp;ERFS_MEASURE=PI_MD60&amp;GEO=FRANCE-FM&amp;MUN_DENSITY_LEVEL=_T&amp;TPH=_T</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
+          <t>1996-2024 (25 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -1478,86 +1574,96 @@
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
           <t>retenir</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>Préoccupation publique propre (ODD 1.2, sous-objectif enfants de la cible européenne 2030), série annuelle de l'INSEE de 1996 à 2024 (22 points depuis 2000), fiche distincte de la pauvreté d'ensemble (D32).</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="inlineStr">
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>Concept nommé dans le contenu de la dimension (« intensité de la pauvreté »), indicateur ODD 1.i3, publié sans rupture de 1996 à 2024 (25 points).</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr">
         <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R9" s="7" t="inlineStr"/>
-      <c r="S9" s="7" t="inlineStr"/>
+      <c r="T9" s="7" t="inlineStr"/>
+      <c r="U9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>pauvrete_exclusion_arope</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>pauvrete_exclusion_arope</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Personnes en risque de pauvreté ou d'exclusion sociale (AROPE)</t>
+          <t>pauvreté monétaire</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>pauvrete_enfants</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>taux_pauvrete_enfants</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Taux de pauvreté des enfants (moins de 18 ans, seuil à 60 %)</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Part des personnes en risque de pauvreté (moins de 60 % du revenu médian), ou en situation de privation matérielle et sociale sévère, ou vivant dans un ménage à très faible intensité de travail (définition de la …</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
+          <t>Part des personnes de moins de 18 ans vivant dans un ménage dont le niveau de vie est inférieur à 60 % du niveau de vie médian (enquête Revenus fiscaux et sociaux, données non rétropolées, France métropolitaine).</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
           <t>bas</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>% de la population</t>
-        </is>
-      </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Eurostat — sdg_01_10 (indicateur ODD de l'UE, définition 2030 ; doublon ilc_peps01n)</t>
+          <t>% des moins de 18 ans</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>sdg_01_10?freq=A&amp;age=TOTAL&amp;unit=PC&amp;geo=FR</t>
+          <t>INSEE — Melodi DS_ERFS_NON_RETROPOLE (enquête ERFS), mesure PR_MD60, âge Y_LT18, valeurs hors rupture (COMPARE_TIME = NB)</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>2015-2025 (11 points, annuelle)</t>
+          <t>DS_ERFS_NON_RETROPOLE?AGE=Y_LT18&amp;COMPARE_TIME=NB&amp;EMPSTA_ENQ=_T&amp;ERFS_MEASURE=PR_MD60&amp;GEO=FRANCE-FM&amp;PCS=_T&amp;QUANTILE=_T&amp;SEX=_T&amp;TPH=_T</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
+          <t>1996-2024 (22 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
@@ -1567,83 +1673,93 @@
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
           <t>retenir</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr">
-        <is>
-          <t>Indicateur de l'objectif européen et français 2030 (−1,1 million de personnes en France par rapport à 2019, objectifs officiels du référentiel), annuel de 2015 à 2025 (11 points).</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="inlineStr">
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>Préoccupation publique propre (ODD 1.2, sous-objectif enfants de la cible européenne 2030), série annuelle de l'INSEE de 1996 à 2024 (22 points depuis 2000), fiche distincte de la pauvreté d'ensemble (D32).</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
         <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R10" s="7" t="inlineStr"/>
-      <c r="S10" s="7" t="inlineStr"/>
+      <c r="T10" s="7" t="inlineStr"/>
+      <c r="U10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>pauvreté monétaire</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
           <t>pauvrete_monetaire</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>taux_pauvrete_60</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Taux de pauvreté monétaire (seuil à 60 % du niveau de vie médian)</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Part des personnes dont le niveau de vie est inférieur à 60 % du niveau de vie médian (enquête Revenus fiscaux et sociaux, données rétropolées, France métropolitaine, ménages ordinaires).</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>bas</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>% de la population</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>INSEE — Melodi DS_ERFS_RETROPOLE (enquête ERFS, données rétropolées), mesure PR_MD60</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>DS_ERFS_RETROPOLE?AGE=_T&amp;EMPSTA_ENQ=_T&amp;ERFS_MEASURE=PR_MD60&amp;GEO=FRANCE-FM&amp;MUN_DENSITY_LEVEL=_T&amp;TPH=_T</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>1996-2024 (25 points, annuelle)</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -1651,88 +1767,98 @@
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
           <t>retenir</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>Concept présent dans les cinq cadres de référence (§5 du crosswalk, en complément pour l'INSEE), indicateur ODD national 1.i1a, publié sans rupture par l'INSEE de 1996 à 2024 (25 points), un an de plus que la série ODD de la BDM.</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="inlineStr">
+      <c r="S11" s="5" t="inlineStr">
         <is>
           <t>retenu_socle</t>
         </is>
       </c>
-      <c r="R11" s="7" t="inlineStr"/>
-      <c r="S11" s="7" t="inlineStr"/>
+      <c r="T11" s="7" t="inlineStr"/>
+      <c r="U11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>pauvreté monétaire</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
           <t>pauvrete_monetaire</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>taux_pauvrete_50</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Taux de pauvreté monétaire (seuil à 50 % du niveau de vie médian)</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Part des personnes dont le niveau de vie est inférieur à 50 % du niveau de vie médian (enquête Revenus fiscaux et sociaux, données rétropolées, France métropolitaine).</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>bas</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>% de la population</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>INSEE — Melodi DS_ERFS_RETROPOLE (enquête ERFS, données rétropolées), mesure PR_MD50</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>DS_ERFS_RETROPOLE?AGE=_T&amp;EMPSTA_ENQ=_T&amp;ERFS_MEASURE=PR_MD50&amp;GEO=FRANCE-FM&amp;MUN_DENSITY_LEVEL=_T&amp;TPH=_T</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>1996-2024 (25 points, annuelle)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -1745,83 +1871,93 @@
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
+        <is>
           <t>retenir_variante</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr">
+      <c r="R12" s="5" t="inlineStr">
         <is>
           <t>Seuil de pauvreté de l'OCDE (How's Life 1_4) et du Doughnut, publié sans rupture de 1996 à 2024 (25 points), substituable au taux à 60 %, principal de la famille.</t>
         </is>
       </c>
-      <c r="Q12" s="5" t="inlineStr">
+      <c r="S12" s="5" t="inlineStr">
         <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R12" s="7" t="inlineStr"/>
-      <c r="S12" s="7" t="inlineStr"/>
+      <c r="T12" s="7" t="inlineStr"/>
+      <c r="U12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>pauvreté monétaire</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>pauvrete_persistante</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>pauvrete_persistante</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Taux de pauvreté persistante</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Part des personnes dont le revenu disponible équivalent est inférieur au seuil de pauvreté (60 % du médian) l'année courante et au moins deux des trois années précédentes (volet longitudinal d'EU-SILC).</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>bas</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>% de la population</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Eurostat — ilc_li21 (taux de risque persistant de pauvreté, enquêtes EU-SILC)</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>ilc_li21?freq=A&amp;statinfo=MED_EI&amp;rskpovth=B_60&amp;sex=T&amp;age=TOTAL&amp;unit=PC&amp;geo=FR</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>2007-2025 (16 points, annuelle)</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -1834,86 +1970,96 @@
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
+        <is>
           <t>retenir</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr">
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>Seule mesure de la durée de la pauvreté, annuelle sur 2007 et 2011-2025 (16 points depuis 2000), concept distinct du taux annuel.</t>
         </is>
       </c>
-      <c r="Q13" s="5" t="inlineStr">
+      <c r="S13" s="5" t="inlineStr">
         <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R13" s="7" t="inlineStr"/>
-      <c r="S13" s="7" t="inlineStr"/>
+      <c r="T13" s="7" t="inlineStr"/>
+      <c r="U13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>pauvreté ressentie</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
           <t>pauvrete_subjective</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>difficulte_joindre_deux_bouts</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Difficulté à joindre les deux bouts (pauvreté subjective)</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Part des personnes vivant dans un ménage qui déclare arriver à joindre les deux bouts « avec difficulté » ou « avec grande difficulté » (EU-SILC, indicateur de pauvreté subjective).</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>bas</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>% de la population</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Eurostat — ilc_sbjp01 (pauvreté subjective par âge et sexe, EU-SILC)</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>ilc_sbjp01?freq=A&amp;age=TOTAL&amp;sex=T&amp;unit=PC&amp;geo=FR</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>2010-2025 (16 points, annuelle)</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
@@ -1923,86 +2069,96 @@
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
+        <is>
           <t>retenir</t>
         </is>
       </c>
-      <c r="P14" s="5" t="inlineStr">
+      <c r="R14" s="5" t="inlineStr">
         <is>
           <t>Indicateur du cadre Qualité de vie d'Eurostat et de l'OCDE (How's Life 1_5), annuel de 2010 à 2025 (16 points) et raccordable jusqu'en 2004 par sa décomposition publiée.</t>
         </is>
       </c>
-      <c r="Q14" s="5" t="inlineStr">
+      <c r="S14" s="5" t="inlineStr">
         <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R14" s="7" t="inlineStr"/>
-      <c r="S14" s="7" t="inlineStr"/>
+      <c r="T14" s="7" t="inlineStr"/>
+      <c r="U14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>pauvreté ressentie</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
           <t>pauvrete_subjective</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>pauvrete_ressentie</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Part des personnes se considérant comme pauvres (pauvreté ressentie)</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>Part des personnes interrogées par le baromètre d'opinion de la DREES qui répondent « je me considère déjà comme pauvre » à la question PE03 (« pensez-vous qu'il y a un risque que vous deveniez pauvre dans les cinq …</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>bas</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>% des répondants</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>DREES — Baromètre d'opinion de la DREES (data.drees, jeu 431_le-barometre-d-opinion), microdonnées pondérées</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>data.drees.solidarites-sante.gouv.fr, jeu 431_le-barometre-d-opinion, pièces jointes barometre2000_2024_diff_csv et barometre2025_diff_csv ; variable PE03, modalités 3</t>
-        </is>
-      </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
+          <t>data.drees.solidarites-sante.gouv.fr, jeu 431_le-barometre-d-opinion, pièce jointe barometre2000_2025_diff_csv ; variable PE03, modalités 3</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
           <t>2014-2025 (11 points, annuelle)</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
@@ -2012,86 +2168,96 @@
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
+        <is>
           <t>retenir_variante</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr">
+      <c r="R15" s="5" t="inlineStr">
         <is>
           <t>Seule mesure de l'auto-identification comme pauvre (DREES, 11 vagues de 2014 à 2025), autre lecture subjective de la pauvreté, substituable à la difficulté à joindre les deux bouts, principale de la famille.</t>
         </is>
       </c>
-      <c r="Q15" s="5" t="inlineStr">
+      <c r="S15" s="5" t="inlineStr">
         <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R15" s="7" t="inlineStr"/>
-      <c r="S15" s="7" t="inlineStr"/>
+      <c r="T15" s="7" t="inlineStr"/>
+      <c r="U15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>perception_niveau_vie_france</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>pauvrete_percue_hausse</t>
+          <t>pauvreté ressentie</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>pauvrete_subjective</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Part des personnes estimant que la pauvreté a augmenté en France depuis cinq ans</t>
+          <t>preoccupation_pouvoir_achat</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Personnes préoccupées par le niveau des salaires et du pouvoir d'achat (baromètre DREES)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Part des personnes interrogées par le baromètre d'opinion de la DREES qui répondent que la pauvreté et l'exclusion en France « ont augmenté » depuis cinq ans (question PE01, modalité 2), non-réponses incluses au …</t>
+          <t>non</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
+          <t>Part des personnes interrogées par le baromètre d'opinion de la DREES qui se disent « beaucoup » ou « assez » préoccupées par le niveau des salaires et du pouvoir d'achat (question OG04_9 : « Êtes-vous personnellement …</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
           <t>bas</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>% des répondants</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>DREES — Baromètre d'opinion de la DREES (data.drees, jeu 431_le-barometre-d-opinion), microdonnées pondérées</t>
-        </is>
-      </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>data.drees.solidarites-sante.gouv.fr, jeu 431_le-barometre-d-opinion, pièce jointe barometre2000_2025_diff_csv ; variable PE01, modalité 2</t>
+          <t>DREES (baromètre d'opinion) — Baromètre d'opinion de la DREES (data.drees, jeu 431_le-barometre-d-opinion), microdonnées pondérées</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>2000-2025 (25 points, annuelle)</t>
+          <t>data.drees.solidarites-sante.gouv.fr, jeu 431_le-barometre-d-opinion, pièce jointe barometre2000_2025_diff_csv ; variable OG04_9, modalités 1+2</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
+          <t>2014-2025 (12 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr">
@@ -2101,86 +2267,96 @@
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>retenir</t>
+          <t>non</t>
         </is>
       </c>
       <c r="P16" s="5" t="inlineStr">
         <is>
-          <t>Opinion sur la société (D32) portant sur la pauvreté, posée chaque année depuis 2000 sauf en 2003 (25 vagues), calculée sur microdonnées avec un contrôle de plausibilité sur la publication 2025 (D38 b), principale de la famille des perceptions du niveau de vie en France.</t>
+          <t>non</t>
         </is>
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
+          <t>retenir_variante</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>Seule mesure ressentie et annuelle de l'inquiétude pour le pouvoir d'achat, 12 vagues de 2014 à 2025 entre 87,7 % et 90,6 % des répondants, recalculée sur les microdonnées sans valeur publiée pour la recouper (D38 b : au plus retenir_variante).</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R16" s="7" t="inlineStr"/>
-      <c r="S16" s="7" t="inlineStr"/>
+      <c r="T16" s="7" t="inlineStr"/>
+      <c r="U16" s="7" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>perception_niveau_vie_france</t>
+          <t>pauvreté ressentie</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>solde_niveau_vie_france_futur</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Opinion des ménages sur l'évolution future du niveau de vie en France (solde)</t>
+          <t>satisfaction_situation_financiere</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>satisfaction_situation_financiere</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>Satisfaction à l'égard de la situation financière du ménage</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Solde des réponses (part des ménages jugeant que le niveau de vie en France va s'améliorer moins part jugeant qu'il va se détériorer) à la question sur les perspectives d'évolution du niveau de vie en France de …</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
+          <t>Note moyenne (de 0 à 10) donnée par les personnes de 16 ans ou plus à leur satisfaction concernant la situation financière de leur ménage (module bien-être d'EU-SILC).</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
           <t>haut</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>solde d'opinion (points de %)</t>
-        </is>
-      </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>INSEE (enquête de conjoncture auprès des ménages) — BDM, enquête mensuelle de conjoncture auprès des ménages (ENQ-CONJ-MENAGES)</t>
+          <t>note de 0 à 10</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>000857177</t>
+          <t>Eurostat — ilc_pw01b (satisfaction de la vie par domaine, modalité FIN), module ad hoc d'EU-SILC</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>1970-2026 (mensuelle)</t>
+          <t>ilc_pw01b?freq=A&amp;life_sat=FIN&amp;statinfo=AVG&amp;isced11=TOTAL&amp;sex=T&amp;age=Y_GE16&amp;unit=RTG&amp;geo=FR</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
+          <t>2013-2022 (3 points, irreguliere)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
@@ -2190,83 +2366,93 @@
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t>retenir_variante</t>
+          <t>non</t>
         </is>
       </c>
       <c r="P17" s="5" t="inlineStr">
         <is>
-          <t>Solde d'opinion mensuel de l'INSEE depuis 1970 sur les perspectives d'évolution du niveau de vie en France, admis comme variante déclarative par D38 (j), à agréger en moyenne annuelle.</t>
+          <t>non</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>Satisfaction du domaine « niveau de vie » (R4) retenue par le cadre Qualité de vie d'Eurostat, publiée en 2013, 2018 et 2022, série pluriannuelle admise (D17, D28 : écart moyen de 4,5 ans).</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R17" s="7" t="inlineStr"/>
-      <c r="S17" s="7" t="inlineStr"/>
+      <c r="T17" s="7" t="inlineStr"/>
+      <c r="U17" s="7" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>perception_niveau_vie_france</t>
+          <t>privations</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>solde_niveau_vie_france_passe</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Opinion des ménages sur l'évolution passée du niveau de vie en France (solde)</t>
+          <t>privation_materielle_sociale</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>privation_materielle_sociale</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>Taux de privation matérielle et sociale</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Solde des réponses (part des ménages jugeant que le niveau de vie en France s'est amélioré moins part jugeant qu'il s'est détérioré) à la question sur l'évolution passée du niveau de vie en France de l'enquête mensuelle …</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>haut</t>
+          <t>Part des personnes qui déclarent au moins 5 privations parmi 13 (7 relatives au ménage, 6 à la personne : faire face à une dépense imprévue, une semaine de vacances, un repas avec viande ou poisson un jour sur deux, …</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>solde d'opinion (points de %)</t>
+          <t>bas</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>INSEE (enquête de conjoncture auprès des ménages) — BDM, enquête mensuelle de conjoncture auprès des ménages (ENQ-CONJ-MENAGES)</t>
+          <t>% de la population</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>000857176</t>
+          <t>INSEE — BDM, indicateurs ODD (ODD-ERADICATION-PAUVRETE), indicateur 1.i2 et indicateur de richesse nationale n° 7</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>1970-2026 (mensuelle)</t>
+          <t>010594486</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
+          <t>2013-2024 (12 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -2279,83 +2465,93 @@
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>retenir_variante</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="P18" s="5" t="inlineStr">
         <is>
-          <t>Solde d'opinion mensuel de l'INSEE depuis 1970 sur l'évolution passée du niveau de vie en France, admis comme variante déclarative par D38 (j), à agréger en moyenne annuelle.</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>retenu</t>
-        </is>
-      </c>
-      <c r="R18" s="7" t="inlineStr"/>
-      <c r="S18" s="7" t="inlineStr"/>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>Concept présent dans trois cadres (Stiglitz-Sen-Fitoussi, Eurostat, INSEE ; §5 du crosswalk), indicateur de richesse nationale n° 7, publié par l'INSEE de 2013 à 2024 (12 points), INSEE préféré à Eurostat à définition égale.</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>retenu_socle</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr"/>
+      <c r="U18" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>pib_habitant</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>pib_habitant</t>
+          <t>privations</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>privation_materielle_sociale</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>PIB par habitant en volume</t>
+          <t>privation_materielle_sociale_severe</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Taux de privation matérielle et sociale sévère</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Produit intérieur brut rapporté à la population, aux prix de l'année précédente chaînés (euros de l'année de référence 2020 par habitant ; comptes nationaux annuels de l'INSEE, base 2020).</t>
+          <t>non</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>haut</t>
+          <t>Part des personnes qui déclarent au moins 7 privations parmi les 13 éléments de la privation matérielle et sociale (EU-SILC).</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>euros de 2020 par habitant</t>
+          <t>bas</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>INSEE — BDM, comptes nationaux annuels base 2020 (série 011779993)</t>
+          <t>% de la population</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>011779993</t>
+          <t>Eurostat — ilc_mdsd11 (taux de privation matérielle et sociale sévère par âge et sexe ; doublon ODD sdg_01_31)</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>1949-2025 (26 points, annuelle)</t>
+          <t>ilc_mdsd11?freq=A&amp;age=TOTAL&amp;sex=T&amp;unit=PC&amp;geo=FR</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
+          <t>2015-2025 (11 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -2368,86 +2564,96 @@
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>retenir</t>
+          <t>non</t>
         </is>
       </c>
       <c r="P19" s="5" t="inlineStr">
         <is>
-          <t>Indicateur ordinaire de la dimension par décision du gel 1 (A12, R7), série de l'INSEE de 1949 à 2025 (26 points depuis 2000), INSEE préféré à Eurostat (sdg_08_10, en variante) à définition égale.</t>
+          <t>non</t>
         </is>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
+          <t>retenir_variante</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>Composante de l'AROPE et indicateur ODD européen (sdg_01_31), annuel de 2015 à 2025 (11 points), lecture « privation grave » substituable au taux à 5 privations, principal de la famille.</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R19" s="7" t="inlineStr"/>
-      <c r="S19" s="7" t="inlineStr"/>
+      <c r="T19" s="7" t="inlineStr"/>
+      <c r="U19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>production et revenu national</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
           <t>pib_habitant</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>indice_developpement_humain</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Indice de développement humain (IDH)</t>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>pib_habitant</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>PIB par habitant en volume</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Moyenne géométrique de trois indices normalisés : espérance de vie à la naissance, durée de scolarisation (attendue et moyenne) et revenu national brut par habitant en parité de pouvoir d'achat (PNUD).</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
+          <t>Produit intérieur brut rapporté à la population, aux prix de l'année précédente chaînés (euros de l'année de référence 2020 par habitant ; comptes nationaux annuels de l'INSEE, base 2020).</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
           <t>haut</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>indice de 0 à 1</t>
-        </is>
-      </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>PNUD — Rapport sur le développement humain 2025, séries composites (fichier CSV, colonnes hdi_&lt;année&gt;)</t>
+          <t>euros de 2020 par habitant</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>https://hdr.undp.org/sites/default/files/2025_HDR/HDR25_Composite_indices_complete_time_series.csv (colonnes hdi_&lt;année&gt;)</t>
+          <t>INSEE — BDM, comptes nationaux annuels base 2020 (série 011779993)</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>1990-2023 (24 points, annuelle)</t>
+          <t>011779993</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
+          <t>1949-2025 (26 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr">
@@ -2457,83 +2663,93 @@
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>retenir_variante</t>
+          <t>non</t>
         </is>
       </c>
       <c r="P20" s="5" t="inlineStr">
         <is>
-          <t>Composite santé-éducation-revenu couvrant plusieurs dimensions, rattaché à niveau_de_vie comme alternative au PIB par habitant, au plus en variante et jamais au socle (D38 c), annuel de 1990 à 2023 (24 points depuis 2000).</t>
+          <t>non</t>
         </is>
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>Indicateur ordinaire de la dimension par décision du gel 1 (A12, R7), série de l'INSEE de 1949 à 2025 (26 points depuis 2000), INSEE préféré à Eurostat (sdg_08_10, en variante) à définition égale.</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R20" s="7" t="inlineStr"/>
-      <c r="S20" s="7" t="inlineStr"/>
+      <c r="T20" s="7" t="inlineStr"/>
+      <c r="U20" s="7" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>production et revenu national</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
           <t>pib_habitant</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>revenu_national_habitant</t>
-        </is>
-      </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Revenu national brut réel par habitant</t>
+          <t>indice_developpement_humain</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>Indice de développement humain (IDH)</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Revenu national brut (revenus primaires reçus par les résidents, y compris ceux qui viennent du reste du monde) exprimé en termes réels et rapporté à la population (comptes nationaux de l'INSEE, base 2020).</t>
+          <t>non</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
+          <t>Moyenne géométrique de trois indices normalisés : espérance de vie à la naissance, durée de scolarisation (attendue et moyenne) et revenu national brut par habitant en parité de pouvoir d'achat (PNUD).</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
           <t>haut</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>euros par habitant (termes réels selon l'intitulé ; année de référence des prix non trouvée)</t>
-        </is>
-      </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>INSEE — Melodi DD_CNA_AGREGATS (comptes nationaux annuels, base 2020), mesure _RNB_REEL_HABITANT</t>
+          <t>indice de 0 à 1</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>DD_CNA_AGREGATS?ACCOUNTING_ENTRY=B&amp;ACTIVITY=_T&amp;COUNTERPART_AREA=W0&amp;EXPENDITURE=_Z&amp;FREQ=A&amp;GEO=FRANCE-F&amp;INSTR_ASSET=_Z&amp;PRICES=V&amp;PRODUCT=_T&amp;REF_SECTOR=S1&amp;REF_YEAR_PRICE=&amp;STO=_RNB_REEL_HABITANT&amp;TRANSFORMATION=N&amp;UNIT_MEASURE=XDC</t>
+          <t>PNUD — Rapport sur le développement humain 2025, séries composites (fichier CSV, colonnes hdi_&lt;année&gt;)</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>1949-2025 (26 points, annuelle)</t>
+          <t>https://hdr.undp.org/sites/default/files/2025_HDR/HDR25_Composite_indices_complete_time_series.csv (colonnes hdi_&lt;année&gt;)</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
+          <t>1990-2023 (24 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -2541,88 +2757,98 @@
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
           <t>retenir_variante</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr">
-        <is>
-          <t>Alternative au PIB recommandée par Stiglitz-Sen-Fitoussi (revenu national), publiée par l'INSEE de 1949 à 2025 (26 points), substituable au PIB par habitant, principal de la famille.</t>
-        </is>
-      </c>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>Composite santé-éducation-revenu couvrant plusieurs dimensions, rattaché à niveau_de_vie comme alternative au PIB par habitant, au plus en variante et jamais au socle (D38 c), annuel de 1990 à 2023 (24 points depuis 2000).</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R21" s="7" t="inlineStr"/>
-      <c r="S21" s="7" t="inlineStr"/>
+      <c r="T21" s="7" t="inlineStr"/>
+      <c r="U21" s="7" t="inlineStr"/>
     </row>
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>privation_alimentaire</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>privation_alimentaire</t>
+          <t>production et revenu national</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>pib_habitant</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Ne pas avoir les moyens d'un repas avec viande, poisson ou équivalent un jour sur deux</t>
+          <t>revenu_national_habitant</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Revenu national brut réel par habitant</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Part des personnes vivant dans un ménage qui n'a pas les moyens de s'offrir un repas comportant de la viande, du poulet ou du poisson (ou un équivalent végétarien) au moins un jour sur deux (EU-SILC, élément de la …</t>
+          <t>non</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>bas</t>
+          <t>Revenu national brut (revenus primaires reçus par les résidents, y compris ceux qui viennent du reste du monde) exprimé en termes réels et rapporté à la population (comptes nationaux de l'INSEE, base 2020).</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>% de la population</t>
+          <t>haut</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Eurostat — ilc_mdes03 (incapacité à s'offrir un repas comportant de la viande, du poulet ou du poisson un jour sur deux, enquêtes EU-SILC), ensemble des ménages</t>
+          <t>euros par habitant (termes réels selon l'intitulé ; année de référence des prix non trouvée)</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>ilc_mdes03?freq=A&amp;hhcomp=TOTAL&amp;rskpovth=TOTAL&amp;unit=PC&amp;geo=FR</t>
+          <t>INSEE — Melodi DD_CNA_AGREGATS (comptes nationaux annuels, base 2020), mesure _RNB_REEL_HABITANT</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>2004-2025 (22 points, annuelle)</t>
+          <t>DD_CNA_AGREGATS?ACCOUNTING_ENTRY=B&amp;ACTIVITY=_T&amp;COUNTERPART_AREA=W0&amp;EXPENDITURE=_Z&amp;FREQ=A&amp;GEO=FRANCE-F&amp;INSTR_ASSET=_Z&amp;PRICES=V&amp;PRODUCT=_T&amp;REF_SECTOR=S1&amp;REF_YEAR_PRICE=&amp;STO=_RNB_REEL_HABITANT&amp;TRANSFORMATION=N&amp;UNIT_MEASURE=XDC</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
+          <t>1949-2025 (26 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -2635,83 +2861,93 @@
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>retenir</t>
+          <t>non</t>
         </is>
       </c>
       <c r="P22" s="5" t="inlineStr">
         <is>
-          <t>Seule mesure annuelle de l'accès à l'alimentation (A2), publiée par Eurostat de 2004 à 2025 (22 points), plus longue de 6 ans et plus fraîche d'un an que l'indicateur ODD 2.i1 de l'INSEE, dont elle ne s'écarte pas de plus de 0,2 point sur 2010-2024 (méthode §4).</t>
+          <t>non</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
+          <t>retenir_variante</t>
+        </is>
+      </c>
+      <c r="R22" s="5" t="inlineStr">
+        <is>
+          <t>Alternative au PIB recommandée par Stiglitz-Sen-Fitoussi (revenu national), publiée par l'INSEE de 1949 à 2025 (26 points), substituable au PIB par habitant, principal de la famille.</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="inlineStr">
+        <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R22" s="7" t="inlineStr"/>
-      <c r="S22" s="7" t="inlineStr"/>
+      <c r="T22" s="7" t="inlineStr"/>
+      <c r="U22" s="7" t="inlineStr"/>
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>privation_materielle_sociale</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>privation_materielle_sociale</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Taux de privation matérielle et sociale</t>
+          <t>revenus et pouvoir d'achat</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>niveau_vie_median</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>niveau_vie_median</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Niveau de vie médian</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Part des personnes qui déclarent au moins 5 privations parmi 13 (7 relatives au ménage, 6 à la personne : faire face à une dépense imprévue, une semaine de vacances, un repas avec viande ou poisson un jour sur deux, …</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>bas</t>
+          <t>Niveau de vie (revenu disponible du ménage après impôts directs et prestations sociales, divisé par le nombre d'unités de consommation) qui partage la population en deux moitiés, en euros constants de la dernière année …</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>% de la population</t>
+          <t>haut</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>INSEE — BDM, indicateurs ODD (ODD-ERADICATION-PAUVRETE), indicateur 1.i2 et indicateur de richesse nationale n° 7</t>
+          <t>euros constants par an et par unité de consommation</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>010594486</t>
+          <t>INSEE — Melodi DS_ERFS_RETROPOLE (enquête ERFS, données rétropolées), mesure MED_SL</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>2013-2024 (12 points, annuelle)</t>
+          <t>DS_ERFS_RETROPOLE?AGE=_T&amp;EMPSTA_ENQ=_T&amp;ERFS_MEASURE=MED_SL&amp;GEO=FRANCE-FM&amp;MUN_DENSITY_LEVEL=_T&amp;TPH=_T</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
+          <t>1996-2024 (25 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -2719,88 +2955,98 @@
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
           <t>retenir</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr">
-        <is>
-          <t>Concept présent dans trois cadres (Stiglitz-Sen-Fitoussi, Eurostat, INSEE ; §5 du crosswalk), indicateur de richesse nationale n° 7, publié par l'INSEE de 2013 à 2024 (12 points), INSEE préféré à Eurostat à définition égale.</t>
-        </is>
-      </c>
-      <c r="Q23" s="5" t="inlineStr">
+      <c r="R23" s="5" t="inlineStr">
+        <is>
+          <t>Revenu médian des ménages, concept du cadre Qualité de vie d'Eurostat et de Stiglitz-Sen-Fitoussi (§5 du crosswalk), publié sans rupture par l'INSEE de 1996 à 2024 (25 points depuis 2000).</t>
+        </is>
+      </c>
+      <c r="S23" s="5" t="inlineStr">
         <is>
           <t>retenu_socle</t>
         </is>
       </c>
-      <c r="R23" s="7" t="inlineStr"/>
-      <c r="S23" s="7" t="inlineStr"/>
+      <c r="T23" s="7" t="inlineStr"/>
+      <c r="U23" s="7" t="inlineStr"/>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>privation_materielle_sociale</t>
+          <t>revenus et pouvoir d'achat</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>privation_materielle_sociale_severe</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Taux de privation matérielle et sociale sévère</t>
+          <t>niveau_vie_modestes</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>niveau_vie_modestes</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>Niveau de vie des plus modestes (premier décile)</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Part des personnes qui déclarent au moins 7 privations parmi les 13 éléments de la privation matérielle et sociale (EU-SILC).</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>bas</t>
+          <t>Premier décile du niveau de vie : niveau de vie au-dessous duquel vivent les 10 % de personnes les plus modestes, en euros constants (enquête Revenus fiscaux et sociaux, données rétropolées, France métropolitaine).</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>% de la population</t>
+          <t>haut</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Eurostat — ilc_mdsd11 (taux de privation matérielle et sociale sévère par âge et sexe ; doublon ODD sdg_01_31)</t>
+          <t>euros constants par an et par unité de consommation</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>ilc_mdsd11?freq=A&amp;age=TOTAL&amp;sex=T&amp;unit=PC&amp;geo=FR</t>
+          <t>INSEE — Melodi DS_ERFS_RETROPOLE (enquête ERFS, données rétropolées), mesure D1_SL</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>2015-2025 (11 points, annuelle)</t>
+          <t>DS_ERFS_RETROPOLE?AGE=_T&amp;EMPSTA_ENQ=_T&amp;ERFS_MEASURE=D1_SL&amp;GEO=FRANCE-FM&amp;MUN_DENSITY_LEVEL=_T&amp;TPH=_T</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
+          <t>1996-2024 (25 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -2813,83 +3059,93 @@
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
-          <t>retenir_variante</t>
+          <t>non</t>
         </is>
       </c>
       <c r="P24" s="5" t="inlineStr">
         <is>
-          <t>Composante de l'AROPE et indicateur ODD européen (sdg_01_31), annuel de 2015 à 2025 (11 points), lecture « privation grave » substituable au taux à 5 privations, principal de la famille.</t>
+          <t>non</t>
         </is>
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>Seule mesure en euros constants du niveau de vie du bas de la distribution, publiée sans rupture de 1996 à 2024 (25 points depuis 2000), complémentaire du taux de pauvreté qui est relatif au médian.</t>
+        </is>
+      </c>
+      <c r="S24" s="5" t="inlineStr">
+        <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R24" s="7" t="inlineStr"/>
-      <c r="S24" s="7" t="inlineStr"/>
+      <c r="T24" s="7" t="inlineStr"/>
+      <c r="U24" s="7" t="inlineStr"/>
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>revenu_disponible_menages</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>revenu_disponible_ajuste_habitant</t>
+          <t>revenus et pouvoir d'achat</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>niveau_vie_modestes</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Revenu disponible brut ajusté des ménages par habitant, en termes réels</t>
+          <t>pauvrete_ancree_2008</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Taux de pauvreté ancré dans le temps (seuil de 2008)</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Revenu disponible brut des ménages et des institutions sans but lucratif à leur service, augmenté des transferts sociaux en nature (santé, éducation, logement social…), rapporté à la population et exprimé en termes …</t>
+          <t>non</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>haut</t>
+          <t>Part des personnes dont le revenu disponible équivalent est inférieur au seuil de pauvreté de 2008 (60 % du revenu médian de 2008), réévalué de l'inflation (EU-SILC).</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>euros réels par habitant</t>
+          <t>bas</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Eurostat — nasa_10_nf_tr (opérations non financières des comptes de secteur), na_item B7G_R_HAB, secteur S14_S15</t>
+          <t>% de la population</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>nasa_10_nf_tr?freq=A&amp;unit=CP_MNAC&amp;direct=RECV&amp;na_item=B7G_R_HAB&amp;sector=S14_S15&amp;geo=FR</t>
+          <t>Eurostat — ilc_li22b (taux de risque de pauvreté ancré en 2008, enquêtes EU-SILC)</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>2000-2024 (25 points, annuelle)</t>
+          <t>ilc_li22b?freq=A&amp;statinfo=MED_EI&amp;unit=PC&amp;rskpovth=B_60&amp;sex=T&amp;age=TOTAL&amp;geo=FR</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
+          <t>2008-2025 (18 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -2897,88 +3153,98 @@
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
-          <t>retenir</t>
+          <t>non</t>
         </is>
       </c>
       <c r="P25" s="5" t="inlineStr">
         <is>
-          <t>Concept retenu par Stiglitz-Sen-Fitoussi, l'OCDE (1_1) et Eurostat (« revenu disponible des ménages », §5 du crosswalk) et seule série des catalogues en niveau réel par habitant, annuelle de 2000 à 2024 (25 points).</t>
+          <t>non</t>
         </is>
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>retenu_socle</t>
-        </is>
-      </c>
-      <c r="R25" s="7" t="inlineStr"/>
-      <c r="S25" s="7" t="inlineStr"/>
+          <t>retenir_variante</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>Indicateur de pauvreté « absolue » du cadre Qualité de vie d'Eurostat, annuel de 2008 à 2025 (18 points), lecture en taux du premier décile en euros constants, principal de la famille, mais dont la hausse tient aux ruptures d'EU-SILC de 2020 et 2022.</t>
+        </is>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>retenu</t>
+        </is>
+      </c>
+      <c r="T25" s="7" t="inlineStr"/>
+      <c r="U25" s="7" t="inlineStr"/>
     </row>
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>revenus et pouvoir d'achat</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
           <t>revenu_disponible_menages</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>pouvoir_achat_uc</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Évolution du pouvoir d'achat du revenu disponible brut par unité de consommation</t>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>revenu_disponible_ajuste_habitant</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>Revenu disponible brut ajusté des ménages par habitant, en termes réels</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Taux de variation annuel, en volume, du revenu disponible brut des ménages rapporté au nombre d'unités de consommation, déflaté par le prix de la dépense de consommation des ménages (comptes nationaux de l'INSEE, base …</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
+          <t>Revenu disponible brut des ménages et des institutions sans but lucratif à leur service, augmenté des transferts sociaux en nature (santé, éducation, logement social…), rapporté à la population et exprimé en termes …</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
           <t>haut</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>% (évolution annuelle)</t>
-        </is>
-      </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>INSEE — Melodi DD_CNA_AGREGATS (comptes nationaux annuels, base 2020), mesure _PAM_UC</t>
+          <t>euros réels par habitant</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>DD_CNA_AGREGATS?ACCOUNTING_ENTRY=_Z&amp;ACTIVITY=_T&amp;COUNTERPART_AREA=W0&amp;EXPENDITURE=_Z&amp;FREQ=A&amp;GEO=FRANCE-F&amp;INSTR_ASSET=_Z&amp;PRICES=V&amp;PRODUCT=_T&amp;REF_SECTOR=S14&amp;REF_YEAR_PRICE=&amp;STO=_PAM_UC&amp;TRANSFORMATION=GY&amp;UNIT_MEASURE=PT</t>
+          <t>Eurostat — nasa_10_nf_tr (opérations non financières des comptes de secteur), na_item B7G_R_HAB, secteur S14_S15</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>1960-2025 (26 points, annuelle)</t>
+          <t>nasa_10_nf_tr?freq=A&amp;unit=CP_MNAC&amp;direct=RECV&amp;na_item=B7G_R_HAB&amp;sector=S14_S15&amp;geo=FR</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
+          <t>2000-2024 (25 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -2991,83 +3257,93 @@
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>retenir_variante</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="P26" s="5" t="inlineStr">
         <is>
-          <t>Mesure de référence du débat public sur le pouvoir d'achat (INSEE, 1960-2025, 26 points depuis 2000), gardée à côté du niveau réel par habitant parce qu'elle se lit en évolution.</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>retenu</t>
-        </is>
-      </c>
-      <c r="R26" s="7" t="inlineStr"/>
-      <c r="S26" s="7" t="inlineStr"/>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="inlineStr">
+        <is>
+          <t>Concept retenu par Stiglitz-Sen-Fitoussi, l'OCDE (1_1) et Eurostat (« revenu disponible des ménages », §5 du crosswalk) et seule série des catalogues en niveau réel par habitant, annuelle de 2000 à 2024 (25 points).</t>
+        </is>
+      </c>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>retenu_socle</t>
+        </is>
+      </c>
+      <c r="T26" s="7" t="inlineStr"/>
+      <c r="U26" s="7" t="inlineStr"/>
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>satisfaction_situation_financiere</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>satisfaction_situation_financiere</t>
+          <t>revenus et pouvoir d'achat</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>revenu_disponible_menages</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Satisfaction à l'égard de la situation financière du ménage</t>
+          <t>pouvoir_achat_uc</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>Évolution du pouvoir d'achat du revenu disponible brut par unité de consommation</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Note moyenne (de 0 à 10) donnée par les personnes de 16 ans ou plus à leur satisfaction concernant la situation financière de leur ménage (module bien-être d'EU-SILC).</t>
+          <t>non</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
+          <t>Taux de variation annuel, en volume, du revenu disponible brut des ménages rapporté au nombre d'unités de consommation, déflaté par le prix de la dépense de consommation des ménages (comptes nationaux de l'INSEE, base …</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
           <t>haut</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>note de 0 à 10</t>
-        </is>
-      </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Eurostat — ilc_pw01b (satisfaction de la vie par domaine, modalité FIN), module ad hoc d'EU-SILC</t>
+          <t>% (évolution annuelle)</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>ilc_pw01b?freq=A&amp;life_sat=FIN&amp;statinfo=AVG&amp;isced11=TOTAL&amp;sex=T&amp;age=Y_GE16&amp;unit=RTG&amp;geo=FR</t>
+          <t>INSEE — Melodi DD_CNA_AGREGATS (comptes nationaux annuels, base 2020), mesure _PAM_UC</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>2013-2022 (3 points, irreguliere)</t>
+          <t>DD_CNA_AGREGATS?ACCOUNTING_ENTRY=_Z&amp;ACTIVITY=_T&amp;COUNTERPART_AREA=W0&amp;EXPENDITURE=_Z&amp;FREQ=A&amp;GEO=FRANCE-F&amp;INSTR_ASSET=_Z&amp;PRICES=V&amp;PRODUCT=_T&amp;REF_SECTOR=S14&amp;REF_YEAR_PRICE=&amp;STO=_PAM_UC&amp;TRANSFORMATION=GY&amp;UNIT_MEASURE=PT</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
+          <t>1960-2025 (26 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
           <t>non</t>
@@ -3080,120 +3356,1332 @@
       </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t>retenir</t>
+          <t>non</t>
         </is>
       </c>
       <c r="P27" s="5" t="inlineStr">
         <is>
-          <t>Satisfaction du domaine « niveau de vie » (R4) retenue par le cadre Qualité de vie d'Eurostat, publiée en 2013, 2018 et 2022, série pluriannuelle admise (D17, D28 : écart moyen de 4,5 ans).</t>
+          <t>non</t>
         </is>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
+          <t>retenir_variante</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="inlineStr">
+        <is>
+          <t>Mesure de référence du débat public sur le pouvoir d'achat (INSEE, 1960-2025, 26 points depuis 2000), gardée à côté du niveau réel par habitant parce qu'elle se lit en évolution.</t>
+        </is>
+      </c>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
           <t>retenu</t>
         </is>
       </c>
-      <c r="R27" s="7" t="inlineStr"/>
-      <c r="S27" s="7" t="inlineStr"/>
+      <c r="T27" s="7" t="inlineStr"/>
+      <c r="U27" s="7" t="inlineStr"/>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t>sécurité économique des ménages</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>capacite_epargne_percue</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>solde_capacite_epargne_actuelle</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Opinion des ménages sur leur capacité d'épargne actuelle (solde)</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Solde des réponses (favorable moins défavorable) à la question sur la capacité actuelle du ménage à épargner, enquête mensuelle de conjoncture auprès des ménages (Camme), France métropolitaine ; moyenne annuelle des 12 …</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>haut</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>solde d'opinion (points de %)</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>INSEE (enquête de conjoncture auprès des ménages) — BDM, enquête mensuelle de conjoncture auprès des ménages (ENQ-CONJ-MENAGES)</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>000857183</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>1970-2026 (mensuelle)</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>resultat</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q28" s="5" t="inlineStr">
+        <is>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R28" s="5" t="inlineStr">
+        <is>
+          <t>Solde d'opinion INSEE depuis 1970 sur la capacité à épargner, seule mesure annuelle et longue de la marge financière ressentie des ménages, rattaché à la sécurité économique par D29 (P8) ; à agréger en moyenne annuelle.</t>
+        </is>
+      </c>
+      <c r="S28" s="5" t="inlineStr">
+        <is>
+          <t>retenu</t>
+        </is>
+      </c>
+      <c r="T28" s="7" t="inlineStr"/>
+      <c r="U28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>sécurité économique des ménages</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>capacite_epargne_percue</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>solde_capacite_epargne_future</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Opinion des ménages sur leur capacité d'épargne future (solde)</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Solde des réponses (amélioration moins détérioration) à la question sur la capacité du ménage à épargner dans les mois à venir, enquête Camme, France métropolitaine ; moyenne annuelle à calculer.</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>haut</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>solde d'opinion (points de %)</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>INSEE (enquête de conjoncture auprès des ménages) — BDM, enquête mensuelle de conjoncture auprès des ménages (ENQ-CONJ-MENAGES)</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>000857186</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>1972-2026 (mensuelle)</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>resultat</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>retenir_variante</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>Même enquête (1972-2026), mais porte sur une anticipation : variante de la capacité d'épargne actuelle (D29, P8).</t>
+        </is>
+      </c>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>retenu</t>
+        </is>
+      </c>
+      <c r="T29" s="7" t="inlineStr"/>
+      <c r="U29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>sécurité économique des ménages</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>charge_remboursement_dettes</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>charge_remboursement_dettes_lourde</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Remboursement de crédits ou de prêts ressenti comme une lourde charge</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Part des personnes vivant dans un ménage qui déclare que le remboursement de dettes liées à des achats à crédit ou à des prêts représente une lourde charge financière (EU-SILC, volet français SRCV ; autres réponses : …</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>bas</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>% de la population concernée</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Eurostat (EU-SILC ; enquête SRCV de l'INSEE) — ilc_mded05 — Charge financière du remboursement de dettes résultant d'achats à crédit ou de prêts</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>ilc_mded05?freq=A&amp;hhcomp=TOTAL&amp;rskpovth=TOTAL&amp;lev_bur=HVY&amp;unit=PC&amp;geo=FR</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>2004-2025 (22 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>resultat</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q30" s="5" t="inlineStr">
+        <is>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="inlineStr">
+        <is>
+          <t>Seule mesure du poids ressenti des remboursements de crédits, annuelle de 2004 à 2025 (22 points, 23,1 % en 2004, 27,8 % en 2014, 23,0 % en 2025), ruptures signalées en 2020 et 2022.</t>
+        </is>
+      </c>
+      <c r="S30" s="5" t="inlineStr">
+        <is>
+          <t>retenu</t>
+        </is>
+      </c>
+      <c r="T30" s="7" t="inlineStr"/>
+      <c r="U30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>sécurité économique des ménages</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>depense_imprevue</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>depense_imprevue</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Population incapable de faire face à une dépense imprévue</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Part de la population vivant dans un ménage qui déclare ne pas pouvoir faire face, sur ses propres ressources, à une dépense imprévue d'un montant donné (fixé par pays, proche du seuil mensuel de pauvreté) (EU-SILC, …</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>bas</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>% de la population</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Eurostat (EU-SILC ; enquête SRCV de l'INSEE) — ilc_mdes04 — Incapacité à faire face à des dépenses financières imprévues</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>ilc_mdes04?freq=A&amp;hhcomp=TOTAL&amp;rskpovth=TOTAL&amp;unit=PC&amp;geo=FR</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>2004-2025 (22 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>resultat</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="inlineStr">
+        <is>
+          <t>Indicateur phare de la sécurité économique (Eurostat QoL ; SSF, OCDE), annuel 2004-2025 sans lacune (34,2 % en 2004, 28,8 % en 2025), ruptures signalées en 2020 et 2022.</t>
+        </is>
+      </c>
+      <c r="S31" s="5" t="inlineStr">
+        <is>
+          <t>retenu_socle</t>
+        </is>
+      </c>
+      <c r="T31" s="7" t="inlineStr"/>
+      <c r="U31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>sécurité économique des ménages</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>endettement_menages</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>endettement_menages</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Taux d'endettement brut des ménages (dette rapportée au revenu disponible brut)</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Encours des crédits contractés par les ménages (engagements AF4 des comptes financiers) rapporté à leur revenu disponible brut, corrigé de la variation des droits à pension (B6G + D8 net), en pourcentage (comptes …</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>bas</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>% du revenu disponible brut</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Eurostat (comptes nationaux de secteur, d'après l'INSEE et la Banque de France) — nasa_10_ki — Principaux indicateurs des comptes de secteurs, données annuelles</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>nasa_10_ki?freq=A&amp;unit=PC&amp;na_item=DIR_S14&amp;sector=S14&amp;geo=FR</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>2000-2024 (25 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>pression</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q32" s="5" t="inlineStr">
+        <is>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="inlineStr">
+        <is>
+          <t>Mesure de référence de l'endettement des ménages rattachée à la sécurité économique par D39, annuelle de 2000 à 2024 (25 points, 57,3 % en 2000, 104,9 % en 2021, 93,6 % en 2024 provisoire).</t>
+        </is>
+      </c>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>retenu</t>
+        </is>
+      </c>
+      <c r="T32" s="7" t="inlineStr"/>
+      <c r="U32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>sécurité économique des ménages</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>epargne_precaution</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>pauvrete_actifs_liquides</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Pauvreté en actifs financiers liquides (épargne de précaution insuffisante)</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Part de la population dont les actifs financiers liquides (dépôts, épargne disponible), par unité de consommation, sont inférieurs à trois mois de revenu au seuil de pauvreté relative (OCDE, base How's Life?, mesure …</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>bas</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>% de la population</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>OCDE (base How's Life?, d'après les enquêtes patrimoine) — How's Life? (base du bien-être)</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>OECD.WISE.WDP,DSD_HSL@DF_HSL_CWB,1.1 MEASURE=1_6 UNIT_MEASURE=PT_POP</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>2009-2020 (4 points, irreguliere)</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>resultat</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="inlineStr">
+        <is>
+          <t>Seule mesure de l'épargne de précaution, indicateur OCDE 1_6 (35,9 % en 2020), mais 4 valeurs seulement (2009, 2014, 2017, 2020) : report de la dernière valeur (D17).</t>
+        </is>
+      </c>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>retenu</t>
+        </is>
+      </c>
+      <c r="T33" s="7" t="inlineStr"/>
+      <c r="U33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>sécurité économique des ménages</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>insecurite_economique_ressentie</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>risque_pauvrete_ressenti</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Personnes estimant risquer de devenir pauvres dans les cinq ans (baromètre DREES)</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Part des adultes résidant en France métropolitaine (âge minimal à vérifier) qui répondent « oui, plutôt » à la question PE03 du baromètre d'opinion de la DREES (« pensez-vous qu'il y a un risque que vous deveniez pauvre …</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>bas</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>% des répondants</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>DREES (baromètre d'opinion) — Baromètre d'opinion (microdonnées pondérées, data.drees)</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>data.drees.solidarites-sante.gouv.fr, jeu 431_le-barometre-d-opinion, pièce jointe barometre2000_2025_diff_csv ; variable PE03, modalités 1</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>2014-2025 (11 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>resultat</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>Seule série annuelle de la crainte de devenir pauvre (DREES, 11 vagues de 2014 à 2025), la réponse « déjà pauvre » relevant de niveau_de_vie (NDV-4) ; sa baisse (32,1 % en 2014, 16,1 % en 2025) se retrouve parmi les répondants qui ne se disent pas déjà pauvres (34,9 % puis 19,5 %), si bien qu'elle ne tient pas seulement au passage vers la pauvreté ressentie.</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>retenu</t>
+        </is>
+      </c>
+      <c r="T34" s="7" t="inlineStr"/>
+      <c r="U34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>sécurité économique des ménages</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>retards_paiement</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>retards_paiement</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Population en retard de paiement (prêt immobilier, loyer, factures, crédit)</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Part de la population vivant dans un ménage qui a eu, au cours des 12 derniers mois, au moins un retard de paiement de remboursement de prêt immobilier ou de loyer, de factures courantes (énergie, eau…) ou de …</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>bas</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>% de la population</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Eurostat (EU-SILC ; enquête SRCV de l'INSEE) — ilc_mdes05 — Arriérés (remboursement hypothécaire ou de loyer, factures courantes ou achats à tempérament) depuis 2003</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>ilc_mdes05?freq=A&amp;hhcomp=TOTAL&amp;rskpovth=TOTAL&amp;unit=PC&amp;geo=FR</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>2004-2025 (22 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>resultat</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>Indicateur du cadre Eurostat QoL (sécurité économique), annuel 2004-2025 sans lacune (12,7 % en 2004, 8,4 % en 2019, 10,4 % en 2025), ruptures signalées en 2020 et 2022.</t>
+        </is>
+      </c>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>retenu</t>
+        </is>
+      </c>
+      <c r="T35" s="7" t="inlineStr"/>
+      <c r="U35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>sécurité économique des ménages</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>situation_financiere_percue</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>solde_situation_financiere_passee</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Opinion des ménages sur l'évolution passée de leur situation financière (solde)</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Solde des réponses (part des ménages déclarant une amélioration moins part déclarant une détérioration) à la question sur l'évolution de leur situation financière personnelle au cours des douze derniers mois, enquête …</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>haut</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>solde d'opinion (points de %)</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>INSEE (enquête de conjoncture auprès des ménages) — BDM, enquête mensuelle de conjoncture auprès des ménages (ENQ-CONJ-MENAGES)</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>000857184</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>1970-2026 (mensuelle)</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>resultat</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>Solde d'opinion mensuel de l'INSEE depuis 1970 sur l'évolution de la situation financière personnelle, rattaché à la sécurité économique par D29 (P8) ; à agréger en moyenne annuelle.</t>
+        </is>
+      </c>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>retenu</t>
+        </is>
+      </c>
+      <c r="T36" s="7" t="inlineStr"/>
+      <c r="U36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>sécurité économique des ménages</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>situation_financiere_percue</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>solde_situation_financiere_future</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Opinion des ménages sur les perspectives de leur situation financière (solde)</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Solde des réponses (amélioration moins détérioration) à la question sur l'évolution attendue de leur situation financière personnelle au cours des douze prochains mois, enquête Camme, France métropolitaine ; moyenne …</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>haut</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>solde d'opinion (points de %)</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>INSEE (enquête de conjoncture auprès des ménages) — BDM, enquête mensuelle de conjoncture auprès des ménages (ENQ-CONJ-MENAGES)</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>000857185</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>1970-2026 (mensuelle)</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>resultat</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>ecarter</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>Écartée par Léo au gel 2 de securite (D49, classeur du 17/10/2026) : anticipation de la situation financière, variante de la situation passée (1970-2026, D29, P8).</t>
+        </is>
+      </c>
+      <c r="S37" s="5" t="inlineStr">
+        <is>
+          <t>ecarte</t>
+        </is>
+      </c>
+      <c r="T37" s="7" t="inlineStr">
+        <is>
+          <t>ecarte</t>
+        </is>
+      </c>
+      <c r="U37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>sécurité économique des ménages</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>surendettement</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>surendettement</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Situations de surendettement soumises aux commissions (nombre de dossiers)</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Nombre de dossiers de surendettement déposés dans l'année auprès des commissions de surendettement de la Banque de France, France métropolitaine (indicateur national ODD 1.i5).</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>bas</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>nombre de dossiers déposés</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>INSEE (indicateurs ODD, d'après la Banque de France) — BDM, indicateurs ODD (ODD-ERADICATION-PAUVRETE)</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>010594499</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>2010-2024 (15 points, annuelle)</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>resultat</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>Seule mesure administrative des ménages en grande difficulté financière, publiée en nombre par l'INSEE (indicateur national ODD 1.i5), annuelle 2010-2024 (218 102 dossiers en 2010, 108 748 en 2020, 134 807 en 2024).</t>
+        </is>
+      </c>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>retenu</t>
+        </is>
+      </c>
+      <c r="T38" s="7" t="inlineStr"/>
+      <c r="U38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>épargne et patrimoine</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>patrimoine_menages</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>patrimoine_net_median</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Patrimoine net médian des ménages</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Patrimoine net (actifs immobiliers, financiers et professionnels moins les dettes, hors « reste » : véhicules, équipement, objets de valeur) au-dessous duquel se situe la moitié des ménages, en euros constants (enquête …</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>haut</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>euros constants par ménage</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>INSEE — Melodi DS_ENQPAT_DET (détention et montants du patrimoine des ménages), mesure MT_PATNET_HR_CST, médiane (D5), comparable depuis 2010</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>DS_ENQPAT_DET?AGE=_T&amp;COMPARE_TIME=1_2010&amp;DEG_URB_UNIT=_T&amp;ENQPAT_MEASURE=MT_PATNET_HR_CST&amp;GEO=FRANCE-FM&amp;PCS=_T&amp;QUANTILE=D5&amp;QUANTILE_MEASURE=PATNET_HR_CST&amp;TPH=_T</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>2010-2024 (5 points, irreguliere)</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>resultat</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>retenir</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>Seule mesure du patrimoine du ménage médian (Stiglitz-Sen-Fitoussi, OCDE 1_3), cinq vagues de 2010 à 2024 admises comme série pluriannuelle (D17, D28 : écart moyen de 3,5 ans).</t>
+        </is>
+      </c>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>retenu_socle</t>
+        </is>
+      </c>
+      <c r="T39" s="7" t="inlineStr"/>
+      <c r="U39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>épargne et patrimoine</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
           <t>taux_epargne_menages</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>taux_epargne_menages</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Taux d'épargne des ménages</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>Part du revenu disponible brut des ménages qui n'est pas consacrée à la consommation (épargne brute / revenu disponible brut, comptes nationaux de l'INSEE, base 2020).</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>ambigu</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>% du revenu disponible brut</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>INSEE — Melodi DD_CNA_AGREGATS (comptes nationaux annuels, base 2020), mesure _TEM</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>DD_CNA_AGREGATS?ACCOUNTING_ENTRY=_Z&amp;ACTIVITY=_T&amp;COUNTERPART_AREA=W0&amp;EXPENDITURE=_Z&amp;FREQ=A&amp;GEO=FRANCE-F&amp;INSTR_ASSET=_Z&amp;PRICES=V&amp;PRODUCT=_T&amp;REF_SECTOR=S14&amp;REF_YEAR_PRICE=&amp;STO=_TEM&amp;TRANSFORMATION=N&amp;UNIT_MEASURE=PT</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>1949-2025 (26 points, annuelle)</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>resultat</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="O28" s="5" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>ecarter</t>
         </is>
       </c>
-      <c r="P28" s="5" t="inlineStr">
+      <c r="R40" s="5" t="inlineStr">
         <is>
           <t>Sens ambigu : le taux bondit quand la consommation est contrainte (20,03 % en 2020 contre 14,24 % en 2019 pour les ménages et les ISBLSM selon Eurostat, confinements) aussi bien que quand les ménages s'enrichissent.</t>
         </is>
       </c>
-      <c r="Q28" s="5" t="inlineStr">
+      <c r="S40" s="5" t="inlineStr">
         <is>
           <t>ecarte</t>
         </is>
       </c>
-      <c r="R28" s="7" t="inlineStr"/>
-      <c r="S28" s="7" t="inlineStr"/>
+      <c r="T40" s="7" t="inlineStr"/>
+      <c r="U40" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S28"/>
-  <conditionalFormatting sqref="A2:S28">
+  <autoFilter ref="A1:U40"/>
+  <conditionalFormatting sqref="A2:U40">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$R2&lt;&gt;""</formula>
+      <formula>$T2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="R2:R28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur non admise" error="Choisissez une valeur dans la liste : retenu, retenu_socle, ecarte, a_discuter" type="list">
+    <dataValidation sqref="T2:T40" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur non admise" error="Choisissez une valeur dans la liste : retenu, retenu_socle, ecarte, a_discuter" type="list">
       <formula1>"retenu,retenu_socle,ecarte,a_discuter"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3208,11 +4696,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3234,7 +4724,7 @@
         </is>
       </c>
       <c r="B2" s="9">
-        <f>COUNTA(Validation!$B$2:$B$28)</f>
+        <f>COUNTA(Validation!$C$2:$C$40)</f>
         <v/>
       </c>
     </row>
@@ -3245,7 +4735,7 @@
         </is>
       </c>
       <c r="B3" s="9">
-        <f>SUMPRODUCT((Validation!$A$2:$A$28&lt;&gt;"")/COUNTIF(Validation!$A$2:$A$28,Validation!$A$2:$A$28&amp;""))</f>
+        <f>SUMPRODUCT((Validation!$B$2:$B$40&lt;&gt;"")/COUNTIF(Validation!$B$2:$B$40,Validation!$B$2:$B$40&amp;""))</f>
         <v/>
       </c>
     </row>
@@ -3268,7 +4758,7 @@
         </is>
       </c>
       <c r="B6" s="9">
-        <f>COUNTIF(Validation!$O$2:$O$28,"retenir")</f>
+        <f>COUNTIF(Validation!$Q$2:$Q$40,"retenir")</f>
         <v/>
       </c>
     </row>
@@ -3279,7 +4769,7 @@
         </is>
       </c>
       <c r="B7" s="9">
-        <f>COUNTIF(Validation!$O$2:$O$28,"retenir_variante")</f>
+        <f>COUNTIF(Validation!$Q$2:$Q$40,"retenir_variante")</f>
         <v/>
       </c>
     </row>
@@ -3290,7 +4780,7 @@
         </is>
       </c>
       <c r="B8" s="9">
-        <f>COUNTIF(Validation!$O$2:$O$28,"ecarter")</f>
+        <f>COUNTIF(Validation!$Q$2:$Q$40,"ecarter")</f>
         <v/>
       </c>
     </row>
@@ -3301,116 +4791,381 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
+          <t>Socle proposé par l'agent (D41)</t>
+        </is>
+      </c>
+      <c r="B10" s="9">
+        <f>COUNTIF(Validation!$P$2:$P$40,"oui")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr"/>
+      <c r="B11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
           <t>Décisions par défaut</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  retenu_socle</t>
-        </is>
-      </c>
-      <c r="B11" s="9">
-        <f>COUNTIF(Validation!$Q$2:$Q$28,"retenu_socle")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  retenu</t>
-        </is>
-      </c>
-      <c r="B12" s="9">
-        <f>COUNTIF(Validation!$Q$2:$Q$28,"retenu")</f>
-        <v/>
-      </c>
+      <c r="B12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ecarte</t>
+          <t xml:space="preserve">  retenu_socle</t>
         </is>
       </c>
       <c r="B13" s="9">
-        <f>COUNTIF(Validation!$Q$2:$Q$28,"ecarte")</f>
+        <f>COUNTIF(Validation!$S$2:$S$40,"retenu_socle")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  retenu</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
+        <f>COUNTIF(Validation!$S$2:$S$40,"retenu")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ecarte</t>
+        </is>
+      </c>
+      <c r="B15" s="9">
+        <f>COUNTIF(Validation!$S$2:$S$40,"ecarte")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">  a_discuter</t>
         </is>
       </c>
-      <c r="B14" s="9">
-        <f>COUNTIF(Validation!$Q$2:$Q$28,"a_discuter")</f>
+      <c r="B16" s="9">
+        <f>COUNTIF(Validation!$S$2:$S$40,"a_discuter")</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr"/>
-      <c r="B15" s="9" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Vos décisions saisies (exceptions)</t>
         </is>
       </c>
-      <c r="B16" s="9">
-        <f>COUNTA(Validation!$R$2:$R$28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  dont retenu_socle</t>
-        </is>
-      </c>
-      <c r="B17" s="9">
-        <f>COUNTIF(Validation!$R$2:$R$28,"retenu_socle")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  dont retenu</t>
-        </is>
-      </c>
       <c r="B18" s="9">
-        <f>COUNTIF(Validation!$R$2:$R$28,"retenu")</f>
+        <f>COUNTA(Validation!$T$2:$T$40)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  dont ecarte</t>
+          <t xml:space="preserve">  dont retenu_socle</t>
         </is>
       </c>
       <c r="B19" s="9">
-        <f>COUNTIF(Validation!$R$2:$R$28,"ecarte")</f>
+        <f>COUNTIF(Validation!$T$2:$T$40,"retenu_socle")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  dont retenu</t>
+        </is>
+      </c>
+      <c r="B20" s="9">
+        <f>COUNTIF(Validation!$T$2:$T$40,"retenu")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  dont ecarte</t>
+        </is>
+      </c>
+      <c r="B21" s="9">
+        <f>COUNTIF(Validation!$T$2:$T$40,"ecarte")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">  dont a_discuter</t>
         </is>
       </c>
-      <c r="B20" s="9">
-        <f>COUNTIF(Validation!$R$2:$R$28,"a_discuter")</f>
+      <c r="B22" s="9">
+        <f>COUNTIF(Validation!$T$2:$T$40,"a_discuter")</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Socle par sous-thème (D41)</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Fiches</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>retenu_socle par défaut</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>retenu_socle après vos décisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>accès à l'alimentation</t>
+        </is>
+      </c>
+      <c r="B25" s="9">
+        <f>COUNTIF(Validation!$A$2:$A$40,$A25)</f>
+        <v/>
+      </c>
+      <c r="C25" s="9">
+        <f>COUNTIFS(Validation!$A$2:$A$40,$A25,Validation!$S$2:$S$40,"retenu_socle")</f>
+        <v/>
+      </c>
+      <c r="D25" s="9">
+        <f>SUMPRODUCT((Validation!$A$2:$A$40=$A25)*(((Validation!$T$2:$T$40="")*(Validation!$S$2:$S$40="retenu_socle"))+(Validation!$T$2:$T$40="retenu_socle")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>consommation</t>
+        </is>
+      </c>
+      <c r="B26" s="9">
+        <f>COUNTIF(Validation!$A$2:$A$40,$A26)</f>
+        <v/>
+      </c>
+      <c r="C26" s="9">
+        <f>COUNTIFS(Validation!$A$2:$A$40,$A26,Validation!$S$2:$S$40,"retenu_socle")</f>
+        <v/>
+      </c>
+      <c r="D26" s="9">
+        <f>SUMPRODUCT((Validation!$A$2:$A$40=$A26)*(((Validation!$T$2:$T$40="")*(Validation!$S$2:$S$40="retenu_socle"))+(Validation!$T$2:$T$40="retenu_socle")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>opinions sur la société</t>
+        </is>
+      </c>
+      <c r="B27" s="9">
+        <f>COUNTIF(Validation!$A$2:$A$40,$A27)</f>
+        <v/>
+      </c>
+      <c r="C27" s="9">
+        <f>COUNTIFS(Validation!$A$2:$A$40,$A27,Validation!$S$2:$S$40,"retenu_socle")</f>
+        <v/>
+      </c>
+      <c r="D27" s="9">
+        <f>SUMPRODUCT((Validation!$A$2:$A$40=$A27)*(((Validation!$T$2:$T$40="")*(Validation!$S$2:$S$40="retenu_socle"))+(Validation!$T$2:$T$40="retenu_socle")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>pauvreté et exclusion</t>
+        </is>
+      </c>
+      <c r="B28" s="9">
+        <f>COUNTIF(Validation!$A$2:$A$40,$A28)</f>
+        <v/>
+      </c>
+      <c r="C28" s="9">
+        <f>COUNTIFS(Validation!$A$2:$A$40,$A28,Validation!$S$2:$S$40,"retenu_socle")</f>
+        <v/>
+      </c>
+      <c r="D28" s="9">
+        <f>SUMPRODUCT((Validation!$A$2:$A$40=$A28)*(((Validation!$T$2:$T$40="")*(Validation!$S$2:$S$40="retenu_socle"))+(Validation!$T$2:$T$40="retenu_socle")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>pauvreté monétaire</t>
+        </is>
+      </c>
+      <c r="B29" s="9">
+        <f>COUNTIF(Validation!$A$2:$A$40,$A29)</f>
+        <v/>
+      </c>
+      <c r="C29" s="9">
+        <f>COUNTIFS(Validation!$A$2:$A$40,$A29,Validation!$S$2:$S$40,"retenu_socle")</f>
+        <v/>
+      </c>
+      <c r="D29" s="9">
+        <f>SUMPRODUCT((Validation!$A$2:$A$40=$A29)*(((Validation!$T$2:$T$40="")*(Validation!$S$2:$S$40="retenu_socle"))+(Validation!$T$2:$T$40="retenu_socle")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>pauvreté ressentie</t>
+        </is>
+      </c>
+      <c r="B30" s="9">
+        <f>COUNTIF(Validation!$A$2:$A$40,$A30)</f>
+        <v/>
+      </c>
+      <c r="C30" s="9">
+        <f>COUNTIFS(Validation!$A$2:$A$40,$A30,Validation!$S$2:$S$40,"retenu_socle")</f>
+        <v/>
+      </c>
+      <c r="D30" s="9">
+        <f>SUMPRODUCT((Validation!$A$2:$A$40=$A30)*(((Validation!$T$2:$T$40="")*(Validation!$S$2:$S$40="retenu_socle"))+(Validation!$T$2:$T$40="retenu_socle")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>privations</t>
+        </is>
+      </c>
+      <c r="B31" s="9">
+        <f>COUNTIF(Validation!$A$2:$A$40,$A31)</f>
+        <v/>
+      </c>
+      <c r="C31" s="9">
+        <f>COUNTIFS(Validation!$A$2:$A$40,$A31,Validation!$S$2:$S$40,"retenu_socle")</f>
+        <v/>
+      </c>
+      <c r="D31" s="9">
+        <f>SUMPRODUCT((Validation!$A$2:$A$40=$A31)*(((Validation!$T$2:$T$40="")*(Validation!$S$2:$S$40="retenu_socle"))+(Validation!$T$2:$T$40="retenu_socle")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>production et revenu national</t>
+        </is>
+      </c>
+      <c r="B32" s="9">
+        <f>COUNTIF(Validation!$A$2:$A$40,$A32)</f>
+        <v/>
+      </c>
+      <c r="C32" s="9">
+        <f>COUNTIFS(Validation!$A$2:$A$40,$A32,Validation!$S$2:$S$40,"retenu_socle")</f>
+        <v/>
+      </c>
+      <c r="D32" s="9">
+        <f>SUMPRODUCT((Validation!$A$2:$A$40=$A32)*(((Validation!$T$2:$T$40="")*(Validation!$S$2:$S$40="retenu_socle"))+(Validation!$T$2:$T$40="retenu_socle")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>revenus et pouvoir d'achat</t>
+        </is>
+      </c>
+      <c r="B33" s="9">
+        <f>COUNTIF(Validation!$A$2:$A$40,$A33)</f>
+        <v/>
+      </c>
+      <c r="C33" s="9">
+        <f>COUNTIFS(Validation!$A$2:$A$40,$A33,Validation!$S$2:$S$40,"retenu_socle")</f>
+        <v/>
+      </c>
+      <c r="D33" s="9">
+        <f>SUMPRODUCT((Validation!$A$2:$A$40=$A33)*(((Validation!$T$2:$T$40="")*(Validation!$S$2:$S$40="retenu_socle"))+(Validation!$T$2:$T$40="retenu_socle")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>sécurité économique des ménages</t>
+        </is>
+      </c>
+      <c r="B34" s="9">
+        <f>COUNTIF(Validation!$A$2:$A$40,$A34)</f>
+        <v/>
+      </c>
+      <c r="C34" s="9">
+        <f>COUNTIFS(Validation!$A$2:$A$40,$A34,Validation!$S$2:$S$40,"retenu_socle")</f>
+        <v/>
+      </c>
+      <c r="D34" s="9">
+        <f>SUMPRODUCT((Validation!$A$2:$A$40=$A34)*(((Validation!$T$2:$T$40="")*(Validation!$S$2:$S$40="retenu_socle"))+(Validation!$T$2:$T$40="retenu_socle")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>épargne et patrimoine</t>
+        </is>
+      </c>
+      <c r="B35" s="9">
+        <f>COUNTIF(Validation!$A$2:$A$40,$A35)</f>
+        <v/>
+      </c>
+      <c r="C35" s="9">
+        <f>COUNTIFS(Validation!$A$2:$A$40,$A35,Validation!$S$2:$S$40,"retenu_socle")</f>
+        <v/>
+      </c>
+      <c r="D35" s="9">
+        <f>SUMPRODUCT((Validation!$A$2:$A$40=$A35)*(((Validation!$T$2:$T$40="")*(Validation!$S$2:$S$40="retenu_socle"))+(Validation!$T$2:$T$40="retenu_socle")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B36" s="8">
+        <f>SUM(B25:B35)</f>
+        <v/>
+      </c>
+      <c r="C36" s="8">
+        <f>SUM(C25:C35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="8">
+        <f>SUM(D25:D35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Les comptes se recalculent à l'ouverture dans Excel.</t>
         </is>
